--- a/config/rules/.history/MMS200MI.xlsx
+++ b/config/rules/.history/MMS200MI.xlsx
@@ -530,6 +530,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -540,6 +541,10 @@
           <t>Mapped from ABCD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +567,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -572,6 +578,10 @@
           <t>Mapped from ABCM</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,6 +604,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -604,6 +615,10 @@
           <t>Mapped from ABFC</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,6 +641,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -636,6 +652,10 @@
           <t>Mapped from ABFM</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,6 +678,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -668,6 +689,10 @@
           <t>Mapped from ACCG</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -690,6 +715,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -700,6 +726,10 @@
           <t>Mapped from ACHK</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -722,6 +752,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -732,6 +763,10 @@
           <t>Mapped from ACMC</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -754,6 +789,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -764,6 +800,10 @@
           <t>Mapped from ACOC</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -786,6 +826,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -796,6 +837,10 @@
           <t>Mapped from ACOM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -818,6 +863,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -828,6 +874,10 @@
           <t>Mapped from M9ACRF</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -850,6 +900,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -860,6 +911,10 @@
           <t>Mapped from ACTI</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -882,6 +937,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -892,6 +948,10 @@
           <t>Mapped from AEQY</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -914,6 +974,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -924,6 +985,10 @@
           <t>Mapped from CCCM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -946,6 +1011,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -956,6 +1022,10 @@
           <t>Mapped from CCI1</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -978,6 +1048,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -988,6 +1059,10 @@
           <t>Mapped from AGDY</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1010,6 +1085,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1020,6 +1096,10 @@
           <t>Mapped from AGHO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1042,6 +1122,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1052,6 +1133,10 @@
           <t>Mapped from AGMI</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1074,6 +1159,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1084,6 +1170,10 @@
           <t>Mapped from ALMT</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1106,6 +1196,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1116,6 +1207,10 @@
           <t>Mapped from ALQC</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1138,6 +1233,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1148,6 +1244,10 @@
           <t>Mapped from ALQT</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1170,6 +1270,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1180,6 +1281,10 @@
           <t>Mapped from ALS1</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1202,6 +1307,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1212,6 +1318,10 @@
           <t>Mapped from M9ALTS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1234,6 +1344,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1244,6 +1355,10 @@
           <t>Mapped from ALUC</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1266,6 +1381,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1276,6 +1392,10 @@
           <t>Mapped from ALUN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1298,6 +1418,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1308,6 +1429,10 @@
           <t>Mapped from AMCS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1330,6 +1455,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1340,6 +1466,10 @@
           <t>Mapped from CRI1</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1362,6 +1492,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1372,6 +1503,10 @@
           <t>Mapped from AMPT</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1394,6 +1529,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1404,6 +1540,10 @@
           <t>Mapped from M9APPR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1426,6 +1566,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1436,6 +1577,10 @@
           <t>Mapped from ARPA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1458,6 +1603,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1468,6 +1614,10 @@
           <t>Mapped from ARPR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1490,6 +1640,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1500,6 +1651,10 @@
           <t>Mapped from ARR1</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1522,6 +1677,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1532,6 +1688,10 @@
           <t>Mapped from ATMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1554,6 +1714,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1564,6 +1725,10 @@
           <t>Mapped from ATMO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1586,6 +1751,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1596,6 +1762,10 @@
           <t>Mapped from M9ATTC</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1618,6 +1788,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1628,6 +1799,10 @@
           <t>Mapped from M9AUGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1650,6 +1825,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1660,6 +1836,10 @@
           <t>Mapped from AUTC</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1682,6 +1862,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1692,6 +1873,10 @@
           <t>Mapped from AVAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1704,11 +1889,13 @@
           <t>AVST</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1719,6 +1906,10 @@
           <t>Mapped from AVST</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1741,6 +1932,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1751,6 +1943,10 @@
           <t>Mapped from AWDY</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1773,6 +1969,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1783,6 +1980,10 @@
           <t>Mapped from BACD</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1805,6 +2006,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1815,6 +2017,10 @@
           <t>Mapped from BBTM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1837,6 +2043,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1847,6 +2054,10 @@
           <t>Mapped from BGRP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1869,6 +2080,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1879,6 +2091,10 @@
           <t>Mapped from BOGR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1901,6 +2117,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1911,6 +2128,10 @@
           <t>Mapped from BPEY</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1933,6 +2154,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1943,6 +2165,10 @@
           <t>Mapped from BUAR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2000,6 +2226,10 @@
           <t>Mapped from BUYE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2022,6 +2252,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2032,6 +2263,10 @@
           <t>Mapped from BYPR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2054,6 +2289,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2064,6 +2300,10 @@
           <t>Mapped from M9CAWC</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2086,6 +2326,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2096,6 +2337,10 @@
           <t>Mapped from CAWT</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2118,6 +2363,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2128,6 +2374,10 @@
           <t>Mapped from CCCM</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2150,6 +2400,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2160,6 +2411,10 @@
           <t>Mapped from CCI1</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2182,6 +2437,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2192,6 +2448,10 @@
           <t>Mapped from CCO1</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2214,6 +2474,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2224,6 +2485,10 @@
           <t>Mapped from CCO2</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2246,6 +2511,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2256,6 +2522,10 @@
           <t>Mapped from CCO3</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2278,6 +2548,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2288,6 +2559,10 @@
           <t>Mapped from CDYN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2310,6 +2585,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2320,6 +2596,10 @@
           <t>Mapped from CETY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2342,6 +2622,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2352,6 +2633,10 @@
           <t>Mapped from CFI1</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2374,6 +2659,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2384,6 +2670,10 @@
           <t>Mapped from CFI2</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2406,6 +2696,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2416,6 +2707,10 @@
           <t>Mapped from CFI3</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2438,6 +2733,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2448,6 +2744,10 @@
           <t>Mapped from CFI4</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2470,6 +2770,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2480,6 +2781,10 @@
           <t>Mapped from CFI5</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2502,6 +2807,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2512,6 +2818,10 @@
           <t>Mapped from CHCD</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2534,6 +2844,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2544,6 +2855,10 @@
           <t>Mapped from M9COCD</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2566,6 +2881,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2576,6 +2892,10 @@
           <t>Mapped from M9COFA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2598,6 +2918,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2608,6 +2929,10 @@
           <t>Mapped from COMG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2630,6 +2955,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2640,6 +2966,10 @@
           <t>Mapped from CONC</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2652,6 +2982,7 @@
           <t>CPCD</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2672,6 +3003,10 @@
           <t>Mapped from CPCD</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2694,6 +3029,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2704,6 +3040,10 @@
           <t>Mapped from M9CPDC</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2726,6 +3066,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2736,6 +3077,10 @@
           <t>Mapped from CPGR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2758,6 +3103,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2768,6 +3114,10 @@
           <t>Mapped from M9CPL0</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2790,6 +3140,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2800,6 +3151,10 @@
           <t>Mapped from M9CPL1</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2822,6 +3177,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2832,6 +3188,10 @@
           <t>Mapped from M9CPL2</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2844,6 +3204,7 @@
           <t>CPRE</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2864,6 +3225,10 @@
           <t>Mapped from M9CPRE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2876,6 +3241,7 @@
           <t>CPRI</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2896,6 +3262,10 @@
           <t>Mapped from M9CPRI</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2918,6 +3288,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2928,6 +3299,10 @@
           <t>Mapped from CPUN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2950,6 +3325,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2960,6 +3336,10 @@
           <t>Mapped from CQUQ</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2982,6 +3362,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2992,6 +3373,10 @@
           <t>Mapped from CRI1</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3014,6 +3399,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3024,6 +3410,10 @@
           <t>Mapped from CRJQ</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3046,6 +3436,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3056,6 +3447,10 @@
           <t>Mapped from M9CRTM</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3078,6 +3473,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3088,6 +3484,10 @@
           <t>Mapped from CSLV</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3110,6 +3510,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3120,6 +3521,10 @@
           <t>Mapped from M9CSNO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3142,6 +3547,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3152,6 +3558,10 @@
           <t>Mapped from CSTQ</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3174,6 +3584,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3184,6 +3595,10 @@
           <t>Mapped from CUCD</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3206,6 +3621,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3216,6 +3632,10 @@
           <t>Mapped from CUCS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3238,6 +3658,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3248,6 +3669,10 @@
           <t>Mapped from CWUN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3270,6 +3695,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3280,6 +3706,10 @@
           <t>Mapped from DCCD</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3302,6 +3732,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3312,6 +3743,10 @@
           <t>Mapped from DDEX</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3334,6 +3769,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3344,6 +3780,10 @@
           <t>Mapped from DDLO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3366,6 +3806,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3376,6 +3817,10 @@
           <t>Mapped from M9DICM</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3398,6 +3843,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3408,6 +3854,10 @@
           <t>Mapped from M9DIDF</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3430,6 +3880,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3440,6 +3891,10 @@
           <t>Mapped from M9DIDY</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3462,6 +3917,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3472,6 +3928,10 @@
           <t>Mapped from DIGI</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3494,6 +3954,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3504,6 +3965,10 @@
           <t>Mapped from DIGR</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3526,6 +3991,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3536,6 +4002,10 @@
           <t>Mapped from DILE</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3558,6 +4028,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3568,6 +4039,10 @@
           <t>Mapped from DIM1</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3590,6 +4065,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3600,6 +4076,10 @@
           <t>Mapped from DIM2</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3622,6 +4102,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3632,6 +4113,10 @@
           <t>Mapped from DIM3</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3654,6 +4139,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3664,6 +4150,10 @@
           <t>Mapped from DIRR</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3686,6 +4176,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3696,6 +4187,10 @@
           <t>Mapped from DITI</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3718,6 +4213,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3728,6 +4224,10 @@
           <t>Mapped from M9DLEF</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3750,6 +4250,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3760,6 +4261,10 @@
           <t>Mapped from M9DLET</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3782,6 +4287,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3792,6 +4298,10 @@
           <t>Mapped from DMFN</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3814,6 +4324,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3824,6 +4335,10 @@
           <t>Mapped from DPID</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3846,6 +4361,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3856,6 +4372,10 @@
           <t>Mapped from DPLO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3878,6 +4398,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3888,6 +4409,10 @@
           <t>Mapped from DWNO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3910,6 +4435,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3920,6 +4446,10 @@
           <t>Mapped from M9ECAR</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3942,6 +4472,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3952,6 +4483,10 @@
           <t>Mapped from M9ECCC</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3974,6 +4509,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3984,6 +4520,10 @@
           <t>Mapped from ECMA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4006,6 +4546,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4016,6 +4557,10 @@
           <t>Mapped from ECVE</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4038,6 +4583,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4048,6 +4594,10 @@
           <t>Mapped from EOQM</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4070,6 +4620,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4080,6 +4631,10 @@
           <t>Mapped from EOQT</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4102,6 +4657,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4112,6 +4668,10 @@
           <t>Mapped from EPCD</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4134,6 +4694,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4144,6 +4705,10 @@
           <t>Mapped from EQDA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4166,6 +4731,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4176,6 +4742,10 @@
           <t>Mapped from ETRF</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4198,6 +4768,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4208,6 +4779,10 @@
           <t>Mapped from EVGR</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4230,6 +4805,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4240,6 +4816,10 @@
           <t>Mapped from EXCA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4262,6 +4842,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4272,6 +4853,10 @@
           <t>Mapped from EXPD</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4309,6 +4894,10 @@
           <t>Mapped from M9FACI</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4321,11 +4910,13 @@
           <t>FANO</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4336,6 +4927,10 @@
           <t>Mapped from M9FANO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4348,11 +4943,13 @@
           <t>FANQ</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4363,6 +4960,10 @@
           <t>Mapped from M9FANQ</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4375,11 +4976,13 @@
           <t>FANR</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4390,6 +4993,10 @@
           <t>Mapped from M9FANR</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4412,6 +5019,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4422,6 +5030,10 @@
           <t>Mapped from M9FATM</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4444,6 +5056,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4454,6 +5067,10 @@
           <t>Mapped from FCCM</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4476,6 +5093,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4486,6 +5104,10 @@
           <t>Mapped from FCU1</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4508,6 +5130,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4518,6 +5141,10 @@
           <t>Mapped from FEBA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4540,6 +5167,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4550,6 +5178,10 @@
           <t>Mapped from FRAG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4572,6 +5204,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4582,6 +5215,10 @@
           <t>Mapped from FRE3</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4604,6 +5241,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4614,6 +5252,10 @@
           <t>Mapped from FRE4</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4636,6 +5278,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4646,6 +5289,10 @@
           <t>Mapped from FSSQ</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4668,6 +5315,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4678,6 +5326,10 @@
           <t>Mapped from FUDS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4700,6 +5352,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4710,6 +5363,10 @@
           <t>Mapped from FUNC</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4732,6 +5389,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4742,6 +5400,10 @@
           <t>Mapped from GRMT</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4764,6 +5426,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4774,6 +5437,10 @@
           <t>Mapped from GRP1</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4796,6 +5463,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4806,6 +5474,10 @@
           <t>Mapped from GRP2</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4828,6 +5500,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4838,6 +5511,10 @@
           <t>Mapped from GRP3</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4860,6 +5537,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4870,6 +5548,10 @@
           <t>Mapped from GRP4</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4892,6 +5574,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4902,6 +5585,10 @@
           <t>Mapped from GRP5</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4924,6 +5611,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4934,6 +5622,10 @@
           <t>Mapped from GRTI</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4956,6 +5648,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4966,6 +5659,10 @@
           <t>Mapped from GRTS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4988,6 +5685,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4998,6 +5696,10 @@
           <t>Mapped from GRWE</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5020,6 +5722,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5030,6 +5733,10 @@
           <t>Mapped from HAC1</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5052,6 +5759,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5062,6 +5770,10 @@
           <t>Mapped from HAC2</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5084,6 +5796,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5094,6 +5807,10 @@
           <t>Mapped from HAC3</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5116,6 +5833,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5126,6 +5844,10 @@
           <t>Mapped from HAZI</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5148,6 +5870,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5158,6 +5881,10 @@
           <t>Mapped from HIE1</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5180,6 +5907,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5190,6 +5918,10 @@
           <t>Mapped from HIE2</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5212,6 +5944,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5222,6 +5955,10 @@
           <t>Mapped from HIE3</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5244,6 +5981,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5254,6 +5992,10 @@
           <t>Mapped from HIE4</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5276,6 +6018,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5286,6 +6029,10 @@
           <t>Mapped from HIE5</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5308,6 +6055,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5318,6 +6066,10 @@
           <t>Mapped from HVMT</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5340,6 +6092,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5350,6 +6103,10 @@
           <t>Mapped from IDDT</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5372,6 +6129,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5382,6 +6140,10 @@
           <t>Mapped from IHEI</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5404,6 +6166,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5414,6 +6177,10 @@
           <t>Mapped from ILEN</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5436,6 +6203,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5446,6 +6214,10 @@
           <t>Mapped from INCD</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5468,6 +6240,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5478,6 +6251,10 @@
           <t>Mapped from INDI</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5500,6 +6277,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5510,6 +6288,10 @@
           <t>Mapped from INDT</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5532,6 +6314,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5542,6 +6325,10 @@
           <t>Mapped from INSC</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5564,6 +6351,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5574,6 +6362,10 @@
           <t>Mapped from INSH</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5596,6 +6388,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5606,6 +6399,10 @@
           <t>Mapped from INSL</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5628,6 +6425,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5638,6 +6436,10 @@
           <t>Mapped from IPLA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5660,6 +6462,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5670,6 +6473,10 @@
           <t>Mapped from ISEG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5692,6 +6499,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5702,6 +6510,10 @@
           <t>Mapped from ITCL</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5724,6 +6536,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5734,6 +6547,10 @@
           <t>Mapped from ITDS</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5756,6 +6573,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5766,6 +6584,10 @@
           <t>Mapped from ITGR</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5788,6 +6610,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5798,6 +6621,10 @@
           <t>Mapped from ITNE</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5837,6 +6664,10 @@
           <t>Mapped from M9ITNO</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5859,6 +6690,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5869,6 +6701,10 @@
           <t>Mapped from ITRF</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5891,6 +6727,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5901,6 +6738,10 @@
           <t>Mapped from ITRU</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5923,6 +6764,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5933,6 +6775,10 @@
           <t>Mapped from ITTY</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5955,6 +6801,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5965,6 +6812,10 @@
           <t>Mapped from IWID</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5987,6 +6838,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5997,6 +6849,10 @@
           <t>Mapped from M9JITF</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6019,6 +6875,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6029,6 +6886,10 @@
           <t>Mapped from KTEX</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6051,6 +6912,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6061,6 +6923,10 @@
           <t>Mapped from M9LAMA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6083,6 +6949,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6093,6 +6960,10 @@
           <t>Mapped from LEA1</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6115,6 +6986,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6125,6 +6997,10 @@
           <t>Mapped from LEA2</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6147,6 +7023,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6157,6 +7034,10 @@
           <t>Mapped from LEA3</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6179,6 +7060,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6189,6 +7071,10 @@
           <t>Mapped from M9LEA4</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6211,6 +7097,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6221,6 +7108,10 @@
           <t>Mapped from LEAI</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6243,6 +7134,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6253,6 +7145,10 @@
           <t>Mapped from LEAT</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6275,6 +7171,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6285,6 +7182,10 @@
           <t>Mapped from LEVD</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6307,6 +7208,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6317,6 +7219,10 @@
           <t>Mapped from LEVL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6339,6 +7245,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6349,6 +7256,10 @@
           <t>Mapped from LOQT</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6361,11 +7272,13 @@
           <t>LYQT</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6376,6 +7289,10 @@
           <t>Mapped from LYQT</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6398,6 +7315,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6408,6 +7326,10 @@
           <t>Mapped from MABC</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6430,6 +7352,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6440,6 +7363,10 @@
           <t>Mapped from MABU</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6462,6 +7389,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6472,6 +7400,10 @@
           <t>Mapped from MAPL</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6494,6 +7426,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6504,6 +7437,10 @@
           <t>Mapped from MAPN</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6526,6 +7463,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6536,6 +7474,10 @@
           <t>Mapped from M9MARC</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6558,6 +7500,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6568,6 +7511,10 @@
           <t>Mapped from MBFR</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6590,6 +7537,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6600,6 +7548,10 @@
           <t>Mapped from MBSR</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6622,6 +7574,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6632,6 +7585,10 @@
           <t>Mapped from MBUR</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6654,6 +7611,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6664,6 +7622,10 @@
           <t>Mapped from MDIR</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6686,6 +7648,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6696,6 +7659,10 @@
           <t>Mapped from MES1</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6718,6 +7685,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6728,6 +7696,10 @@
           <t>Mapped from MES2</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6750,6 +7722,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6760,6 +7733,10 @@
           <t>Mapped from MES3</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6782,6 +7759,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6792,6 +7770,10 @@
           <t>Mapped from MES4</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6814,6 +7796,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6824,6 +7807,10 @@
           <t>Mapped from MOCM</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6846,6 +7833,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6856,6 +7844,10 @@
           <t>Mapped from M9MOLL</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6878,6 +7870,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6888,6 +7881,10 @@
           <t>Mapped from MOQT</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6910,6 +7907,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6920,6 +7918,10 @@
           <t>Mapped from MOTP</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6942,6 +7944,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6952,6 +7955,10 @@
           <t>Mapped from MPCD</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6974,6 +7981,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6984,6 +7992,10 @@
           <t>Mapped from MPCT</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7006,6 +8018,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7016,6 +8029,10 @@
           <t>Mapped from MPGM</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7038,6 +8055,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7048,6 +8066,10 @@
           <t>Mapped from MRQT</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7083,6 +8105,10 @@
           <t>Mapped from MSCH</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7105,6 +8131,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7115,6 +8142,10 @@
           <t>Mapped from MVA1</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7137,6 +8168,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7147,6 +8179,10 @@
           <t>Mapped from MVA2</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7169,6 +8205,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7179,6 +8216,10 @@
           <t>Mapped from MVA3</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7201,6 +8242,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7211,6 +8253,10 @@
           <t>Mapped from MVA4</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7233,6 +8279,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7243,6 +8290,10 @@
           <t>Mapped from MXPC</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7265,6 +8316,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7275,6 +8327,10 @@
           <t>Mapped from MXSM</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7297,6 +8353,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7307,6 +8364,10 @@
           <t>Mapped from MXST</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7329,6 +8390,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7339,6 +8401,10 @@
           <t>Mapped from NESA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7361,6 +8427,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7371,6 +8438,10 @@
           <t>Mapped from NEWE</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7393,6 +8464,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7403,6 +8475,10 @@
           <t>Mapped from NPTO</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7425,6 +8501,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7435,6 +8512,10 @@
           <t>Mapped from NSUF</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7457,6 +8538,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7467,6 +8549,10 @@
           <t>Mapped from NUIN</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7489,6 +8575,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7499,6 +8586,10 @@
           <t>Mapped from NUS7</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7521,6 +8612,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7531,6 +8623,10 @@
           <t>Mapped from ODDT</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7553,6 +8649,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7563,6 +8660,10 @@
           <t>Mapped from M9OPFQ</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7585,6 +8686,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7595,6 +8697,10 @@
           <t>Mapped from OPLC</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7617,6 +8723,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7627,6 +8734,10 @@
           <t>Mapped from OPOM</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7649,6 +8760,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7659,6 +8771,10 @@
           <t>Mapped from M9ORCO</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7681,6 +8797,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7691,6 +8808,10 @@
           <t>Mapped from ORQT</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7713,6 +8834,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7723,6 +8845,10 @@
           <t>Mapped from ORTY</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7745,6 +8871,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7755,6 +8882,10 @@
           <t>Mapped from OTDI</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7777,6 +8908,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7787,6 +8919,10 @@
           <t>Mapped from PAFL</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7809,6 +8945,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7819,6 +8956,10 @@
           <t>Mapped from PDCC</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7841,6 +8982,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7851,6 +8993,10 @@
           <t>Mapped from PDLN</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7873,6 +9019,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7883,6 +9030,10 @@
           <t>Mapped from PEQ1</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7905,6 +9056,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7915,6 +9067,10 @@
           <t>Mapped from PEQ2</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7937,6 +9093,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7947,6 +9104,10 @@
           <t>Mapped from PEQ3</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7969,6 +9130,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7979,6 +9141,10 @@
           <t>Mapped from PEQ4</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8001,6 +9167,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8011,6 +9178,10 @@
           <t>Mapped from PET1</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8033,6 +9204,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8043,6 +9215,10 @@
           <t>Mapped from PET2</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8065,6 +9241,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8075,6 +9252,10 @@
           <t>Mapped from PET3</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8097,6 +9278,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8107,6 +9289,10 @@
           <t>Mapped from PET4</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8129,6 +9315,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8139,6 +9326,10 @@
           <t>Mapped from PFTM</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8161,6 +9352,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8171,6 +9363,10 @@
           <t>Mapped from PISE</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8193,6 +9389,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8203,6 +9400,10 @@
           <t>Mapped from M9PLAP</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8242,6 +9443,10 @@
           <t>Mapped from PLCD</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8264,6 +9469,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8274,6 +9480,10 @@
           <t>Mapped from PLHZ</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8296,6 +9506,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8306,6 +9517,10 @@
           <t>Mapped from PLMZ</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8328,6 +9543,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8338,6 +9554,10 @@
           <t>Mapped from M9PLUP</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8360,6 +9580,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8370,6 +9591,10 @@
           <t>Mapped from POCY</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8392,6 +9617,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8402,6 +9628,10 @@
           <t>Mapped from POOT</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8424,6 +9654,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8434,6 +9665,10 @@
           <t>Mapped from PPDT</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8456,6 +9691,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8466,6 +9702,10 @@
           <t>Mapped from M9PPL0</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8488,6 +9728,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8498,6 +9739,10 @@
           <t>Mapped from M9PPL1</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8520,6 +9765,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8530,6 +9776,10 @@
           <t>Mapped from M9PPL2</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8552,6 +9802,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8562,6 +9813,10 @@
           <t>Mapped from PPUN</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8584,6 +9839,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8594,6 +9850,10 @@
           <t>Mapped from PRCD</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8606,6 +9866,7 @@
           <t>PRCM</t>
         </is>
       </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -8626,6 +9887,10 @@
           <t>Mapped from M9PRCM</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8648,6 +9913,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8658,6 +9924,10 @@
           <t>Mapped from PRGP</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8680,6 +9950,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8690,6 +9961,10 @@
           <t>Mapped from PRGR</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8702,11 +9977,13 @@
           <t>PRIF</t>
         </is>
       </c>
+      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8717,6 +9994,10 @@
           <t>Mapped from PRIF</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8739,6 +10020,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8749,6 +10031,10 @@
           <t>Mapped from PROD</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8771,6 +10057,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8781,6 +10068,10 @@
           <t>Mapped from M9PRRA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8793,16 +10084,15 @@
           <t>PRVG</t>
         </is>
       </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>PYTHON</t>
+          <t>CONST</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>if source is None or str(source).strip() == "":
-    return "NA"
-return source</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -8815,6 +10105,10 @@
           <t>Mapped from PRVG</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8837,6 +10131,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8847,6 +10142,10 @@
           <t>Mapped from PUCD</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8869,6 +10168,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8879,6 +10179,10 @@
           <t>Mapped from PUIT</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8901,6 +10205,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8911,6 +10216,10 @@
           <t>Mapped from PUPR</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8933,6 +10242,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8943,6 +10253,10 @@
           <t>Mapped from PUUN</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8965,6 +10279,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8975,6 +10290,10 @@
           <t>Mapped from QACD</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8997,6 +10316,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9007,6 +10327,10 @@
           <t>Mapped from QIRQ</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9029,6 +10353,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9039,6 +10364,10 @@
           <t>Mapped from QMGP</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9061,6 +10390,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9071,6 +10401,10 @@
           <t>Mapped from M9QUCW</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9093,6 +10427,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9103,6 +10438,10 @@
           <t>Mapped from QUQT</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9125,6 +10464,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9135,6 +10475,10 @@
           <t>Mapped from REDY</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9157,6 +10501,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9167,6 +10512,10 @@
           <t>Mapped from REMN</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9189,6 +10538,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9199,6 +10549,10 @@
           <t>Mapped from REOP</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9221,6 +10575,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9231,6 +10586,10 @@
           <t>Mapped from REQT</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9288,6 +10647,10 @@
           <t>Manual Edit</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9310,6 +10673,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9320,6 +10684,10 @@
           <t>Mapped from M9REWH</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9342,6 +10710,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9352,6 +10721,10 @@
           <t>Mapped from RIDC</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9374,6 +10747,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9384,6 +10758,10 @@
           <t>Mapped from RIDE</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9406,6 +10784,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9416,6 +10795,10 @@
           <t>Mapped from M9RJCW</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9438,6 +10821,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9448,6 +10832,10 @@
           <t>Mapped from RJQT</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9470,6 +10858,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9480,6 +10869,10 @@
           <t>Mapped from RLQT</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9502,6 +10895,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9512,6 +10906,10 @@
           <t>Mapped from RMSG</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9534,6 +10932,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9544,6 +10943,10 @@
           <t>Mapped from RNRI</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9566,6 +10969,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9576,6 +10980,10 @@
           <t>Mapped from RUID</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9598,6 +11006,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9608,6 +11017,10 @@
           <t>Mapped from SACD</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9630,6 +11043,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9640,6 +11054,10 @@
           <t>Mapped from SAEL</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9662,6 +11080,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9672,6 +11091,10 @@
           <t>Mapped from SAFC</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9694,6 +11117,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9704,6 +11128,10 @@
           <t>Mapped from SALE</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9726,6 +11154,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9736,6 +11165,10 @@
           <t>Mapped from SALM</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9758,6 +11191,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9768,6 +11202,10 @@
           <t>Mapped from SAPR</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9790,6 +11228,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9800,6 +11239,10 @@
           <t>Mapped from SATD</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9822,6 +11265,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9832,6 +11276,10 @@
           <t>Mapped from SCGR</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9854,6 +11302,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9864,6 +11313,10 @@
           <t>Mapped from M9SCMO</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9886,6 +11339,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9896,6 +11350,10 @@
           <t>Mapped from SCPO</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9918,6 +11376,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9928,6 +11387,10 @@
           <t>Mapped from SCRQ</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9950,6 +11413,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9960,6 +11424,10 @@
           <t>Mapped from SESO</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9982,6 +11450,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9992,6 +11461,10 @@
           <t>Mapped from SHCC</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10014,6 +11487,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10024,6 +11498,10 @@
           <t>Mapped from SLDY</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10046,6 +11524,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10056,6 +11535,10 @@
           <t>Mapped from SLTP</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10078,6 +11561,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10088,6 +11572,10 @@
           <t>Mapped from SMFI</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10110,6 +11598,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10120,6 +11609,10 @@
           <t>Mapped from M9SOCO</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10132,11 +11625,13 @@
           <t>SODY</t>
         </is>
       </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10147,6 +11642,10 @@
           <t>Mapped from SODY</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10169,6 +11668,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10179,6 +11679,10 @@
           <t>Mapped from SPAC</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10216,6 +11720,10 @@
           <t>Mapped from SPDT</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10238,6 +11746,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10248,6 +11757,10 @@
           <t>Mapped from SPE1</t>
         </is>
       </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10270,6 +11783,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10280,6 +11794,10 @@
           <t>Mapped from SPE2</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10302,6 +11820,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10312,6 +11831,10 @@
           <t>Mapped from SPE3</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10334,6 +11857,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10344,6 +11868,10 @@
           <t>Mapped from SPE4</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10366,6 +11894,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10376,6 +11905,10 @@
           <t>Mapped from SPE5</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10398,6 +11931,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10408,6 +11942,10 @@
           <t>Mapped from SPGV</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10430,6 +11968,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10440,6 +11979,10 @@
           <t>Mapped from SPIH</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10462,6 +12005,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10472,6 +12016,10 @@
           <t>Mapped from SPLC</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10494,6 +12042,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10504,6 +12053,10 @@
           <t>Mapped from SPMT</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10543,6 +12096,10 @@
           <t>Mapped from SPUC</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10565,6 +12122,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10575,6 +12133,10 @@
           <t>Mapped from SPUN</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10597,6 +12159,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10607,6 +12170,10 @@
           <t>Mapped from SQC2</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10629,6 +12196,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10639,6 +12207,10 @@
           <t>Mapped from SQC3</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10661,6 +12233,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10671,6 +12244,10 @@
           <t>Mapped from SQCS</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10693,6 +12270,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10703,6 +12281,10 @@
           <t>Mapped from SSDA</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10725,6 +12307,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10735,6 +12318,10 @@
           <t>Mapped from SSMT</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10757,6 +12344,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10767,6 +12355,10 @@
           <t>Mapped from SSQT</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10789,6 +12381,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10799,6 +12392,10 @@
           <t>Mapped from SSRE</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10811,6 +12408,7 @@
           <t>STAT</t>
         </is>
       </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -10831,6 +12429,10 @@
           <t>Mapped from STAT</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10853,6 +12455,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10863,6 +12466,10 @@
           <t>Mapped from STCD</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10885,6 +12492,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10895,6 +12503,10 @@
           <t>Mapped from STCN</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10917,6 +12529,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10927,6 +12540,10 @@
           <t>Mapped from M9STCW</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10949,6 +12566,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10959,6 +12577,10 @@
           <t>Mapped from STMT</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10981,6 +12603,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10991,6 +12614,10 @@
           <t>Mapped from STNC</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11013,6 +12640,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11023,6 +12651,10 @@
           <t>Mapped from STQT</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11045,6 +12677,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11055,6 +12688,10 @@
           <t>Mapped from STRL</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11077,6 +12714,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11087,6 +12725,10 @@
           <t>Mapped from STTX</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11109,6 +12751,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11119,6 +12762,10 @@
           <t>Mapped from STUN</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11141,6 +12788,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11151,6 +12799,10 @@
           <t>Mapped from SUME</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11173,6 +12825,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11183,6 +12836,10 @@
           <t>Mapped from SUMP</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11220,6 +12877,10 @@
           <t>Mapped from SUNO</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11242,6 +12903,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11252,6 +12914,10 @@
           <t>Mapped from SURT</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11274,6 +12940,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11284,6 +12951,10 @@
           <t>Mapped from SUWH</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11306,6 +12977,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11316,6 +12988,10 @@
           <t>Mapped from SVEI</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11338,6 +13014,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11348,6 +13025,10 @@
           <t>Mapped from TANK</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11370,6 +13051,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11380,6 +13062,10 @@
           <t>Mapped from TAXC</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11402,6 +13088,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11412,6 +13099,10 @@
           <t>Mapped from TBFR</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11434,6 +13125,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11444,6 +13136,10 @@
           <t>Mapped from TBSR</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11466,6 +13162,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11476,6 +13173,10 @@
           <t>Mapped from TBUR</t>
         </is>
       </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11498,6 +13199,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11508,6 +13210,10 @@
           <t>Mapped from TECR</t>
         </is>
       </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11530,6 +13236,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11540,6 +13247,10 @@
           <t>Mapped from TOHI</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11562,6 +13273,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11572,6 +13284,10 @@
           <t>Mapped from TOMU</t>
         </is>
       </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11594,6 +13310,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11604,6 +13321,10 @@
           <t>Mapped from TORE</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11626,6 +13347,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11636,6 +13358,10 @@
           <t>Mapped from TPCD</t>
         </is>
       </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11658,6 +13384,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11668,6 +13395,10 @@
           <t>Mapped from TPLI</t>
         </is>
       </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11690,6 +13421,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11700,6 +13432,10 @@
           <t>Mapped from TRPA</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11712,11 +13448,13 @@
           <t>UCOS</t>
         </is>
       </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11727,6 +13465,10 @@
           <t>Mapped from M9UCOS</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11749,6 +13491,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11759,6 +13502,10 @@
           <t>Mapped from UNMS</t>
         </is>
       </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11781,6 +13528,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11791,6 +13539,10 @@
           <t>Mapped from UNMU</t>
         </is>
       </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11813,6 +13565,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11823,6 +13576,10 @@
           <t>Mapped from UNNN</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11845,6 +13602,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11855,6 +13613,10 @@
           <t>Mapped from UNPA</t>
         </is>
       </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11877,6 +13639,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11887,6 +13650,10 @@
           <t>Mapped from USYE</t>
         </is>
       </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11926,6 +13693,10 @@
           <t>Mapped from M9VAMT</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11948,6 +13719,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11958,6 +13730,10 @@
           <t>Mapped from VOL3</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11980,6 +13756,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11990,6 +13767,10 @@
           <t>Mapped from VTCP</t>
         </is>
       </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12012,6 +13793,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12022,6 +13804,10 @@
           <t>Mapped from VTCS</t>
         </is>
       </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12044,6 +13830,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12054,6 +13841,10 @@
           <t>Mapped from WADY</t>
         </is>
       </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12076,6 +13867,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12086,6 +13878,10 @@
           <t>Mapped from WAL1</t>
         </is>
       </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12108,6 +13904,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12118,6 +13915,10 @@
           <t>Mapped from WAL2</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12140,6 +13941,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12150,6 +13952,10 @@
           <t>Mapped from WAL3</t>
         </is>
       </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12172,6 +13978,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12182,6 +13989,10 @@
           <t>Mapped from WAL4</t>
         </is>
       </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12204,6 +14015,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12214,6 +14026,10 @@
           <t>Mapped from WAPC</t>
         </is>
       </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12236,6 +14052,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12246,6 +14063,10 @@
           <t>Mapped from M9WCLN</t>
         </is>
       </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12268,6 +14089,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12278,6 +14100,10 @@
           <t>Mapped from WHLO</t>
         </is>
       </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12317,6 +14143,10 @@
           <t>Mapped from WHLT</t>
         </is>
       </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12339,6 +14169,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12349,6 +14180,10 @@
           <t>Mapped from WHSL</t>
         </is>
       </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12371,6 +14206,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12381,6 +14217,10 @@
           <t>Mapped from WHSY</t>
         </is>
       </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12403,6 +14243,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12413,6 +14254,10 @@
           <t>Mapped from WHTY</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12435,6 +14280,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12445,6 +14291,10 @@
           <t>Mapped from M9WSCA</t>
         </is>
       </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12467,6 +14317,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12477,6 +14328,10 @@
           <t>Mapped from YEQM</t>
         </is>
       </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12499,6 +14354,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12509,6 +14365,10 @@
           <t>Mapped from YEQT</t>
         </is>
       </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12521,11 +14381,13 @@
           <t>ZCAC</t>
         </is>
       </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12536,6 +14398,10 @@
           <t>Mapped from ZCAC</t>
         </is>
       </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12782,7 +14648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14674,6 +16540,62 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-12 15:24:20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PRVG</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Type: PYTHON-&gt;CONST, Val: 'if source is None or str(source).strip() == "":
+    return "NA"
+return source'-&gt;'"NA"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-12 16:02:38</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PRVG</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Val: '"NA"'-&gt;''</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/rules/.history/MMS200MI.xlsx
+++ b/config/rules/.history/MMS200MI.xlsx
@@ -28,7 +28,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -979,11 +978,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1016,11 +1010,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1053,11 +1042,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1122,11 +1106,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1159,11 +1138,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1708,11 +1682,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1731,6 +1700,11 @@
         </is>
       </c>
       <c r="B39" t="inlineStr">
+        <is>
+          <t>AVST</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>AVST</t>
         </is>
@@ -2629,11 +2603,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2664,11 +2633,6 @@
       <c r="D67" t="inlineStr">
         <is>
           <t>CONST</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3347,11 +3311,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3574,11 +3533,6 @@
       <c r="D95" t="inlineStr">
         <is>
           <t>CONST</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4151,11 +4105,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6169,11 +6118,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6206,11 +6150,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6243,11 +6182,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6344,11 +6278,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6381,11 +6310,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6418,11 +6342,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6477,6 +6396,11 @@
           <t>LYQT</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>LYQT</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -6994,11 +6918,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7191,11 +7110,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7580,11 +7494,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7615,11 +7524,6 @@
       <c r="D219" t="inlineStr">
         <is>
           <t>CONST</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -7758,11 +7662,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7827,11 +7726,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F225" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7856,12 +7750,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ORTY</t>
+          <t>PUIT</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>if row.get("PUIT") == "1": return "NOR"
+if row.get("PUIT") == "2": return "INV"
+if row.get("PUIT") == "3": return "D22"
+return source</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8874,6 +8776,11 @@
           <t>PRIF</t>
         </is>
       </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>PRIF</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -9279,11 +9186,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F269" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9380,11 +9282,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F272" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9415,11 +9312,6 @@
       <c r="D273" t="inlineStr">
         <is>
           <t>CONST</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -9639,11 +9531,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9676,11 +9563,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10001,11 +9883,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F290" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10193,11 +10070,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F296" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10349,6 +10221,11 @@
         </is>
       </c>
       <c r="B301" t="inlineStr">
+        <is>
+          <t>SODY</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
         <is>
           <t>SODY</t>
         </is>
@@ -11234,11 +11111,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F328" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12116,11 +11988,6 @@
       <c r="D355" t="inlineStr">
         <is>
           <t>CONST</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -12721,11 +12588,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F373" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12758,11 +12620,6 @@
           <t>CONST</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F374" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12781,6 +12638,11 @@
         </is>
       </c>
       <c r="B375" t="inlineStr">
+        <is>
+          <t>ZCAC</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
         <is>
           <t>ZCAC</t>
         </is>
@@ -13046,7 +12908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17430,6 +17292,1440 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:40:32</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>STQT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Src: STQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:40:57</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>QUQT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Src: QUQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:07</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>RJQT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Src: RJQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ALQT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Src: ALQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:31</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>AVAL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Src: AVAL-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:37</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>COMG</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Src: COMG-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:41:44</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>COMG</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Val: ''-&gt;'0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:42:16</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ORQT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Src: ORQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:42:22</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>REQT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Src: REQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:42:34</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>RLQT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Src: RLQT-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:51:22</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NUIN</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Src: NUIN-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:21:15</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>USYE</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Src: USYE-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:38:04</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DILE</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Src: DILE-&gt;, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>AGDY</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>AGHO</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AGMI</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ALQC</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ALQT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Src: -&gt;ALQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>AVAL</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Src: -&gt;AVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AVST</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Src: -&gt;AVST</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>COMG</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Src: -&gt;COMG, Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CONC</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DDEX</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DILE</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Src: -&gt;DILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EOQT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LEA1</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LEA2</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LEA3</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LEAT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LEVD</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LEVL</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>LYQT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Src: -&gt;LYQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>MOQT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>MSCH</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NUIN</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Src: -&gt;NUIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NUS7</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OPOM</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ORQT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Src: -&gt;ORQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ORTY</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;PYTHON, Src: ORTY-&gt;PUIT, Val: ''-&gt;'if row.get("PUIT") == "1": return "NOR"
+if row.get("PUIT") == "2": return "INV"
+if row.get("PUIT") == "3": return "D22"
+return source'</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PRIF</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Src: -&gt;PRIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>QUQT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Src: -&gt;QUQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>REOP</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>REQT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Src: -&gt;REQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RJQT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Src: -&gt;RJQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>RLQT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Src: -&gt;RLQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SATD</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SHCC</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SODY</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Src: -&gt;SODY</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>STQT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Src: -&gt;STQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>USYE</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Src: -&gt;USYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>YEQM</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>YEQT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Val: '0'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:13:55</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ZCAC</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Src: -&gt;ZCAC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/rules/.history/MMS200MI.xlsx
+++ b/config/rules/.history/MMS200MI.xlsx
@@ -530,6 +530,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -540,6 +541,10 @@
           <t>Mapped from ABCD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +567,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -572,6 +578,10 @@
           <t>Mapped from ABCM</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,6 +604,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -604,6 +615,10 @@
           <t>Mapped from ABFC</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,6 +641,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -636,6 +652,10 @@
           <t>Mapped from ABFM</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,6 +678,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -668,6 +689,10 @@
           <t>Mapped from ACCG</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -690,6 +715,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -700,6 +726,10 @@
           <t>Mapped from ACHK</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -722,6 +752,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -732,6 +763,10 @@
           <t>Mapped from ACMC</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -754,6 +789,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -764,6 +800,10 @@
           <t>Mapped from ACOC</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -786,6 +826,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -796,6 +837,10 @@
           <t>Mapped from ACOM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -818,6 +863,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -828,6 +874,10 @@
           <t>Mapped from M9ACRF</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -850,6 +900,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -860,6 +911,10 @@
           <t>Mapped from ACTI</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -882,6 +937,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -892,6 +948,10 @@
           <t>Mapped from AEQY</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -914,6 +974,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -924,6 +985,10 @@
           <t>Mapped from CCCM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -946,6 +1011,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -956,6 +1022,10 @@
           <t>Mapped from CCI1</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -978,6 +1048,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -988,6 +1059,10 @@
           <t>Mapped from AGDY</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1010,6 +1085,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1020,6 +1096,10 @@
           <t>Mapped from AGHO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1042,6 +1122,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1052,6 +1133,10 @@
           <t>Mapped from AGMI</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1074,6 +1159,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1084,6 +1170,10 @@
           <t>Mapped from ALMT</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1106,6 +1196,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1116,6 +1207,10 @@
           <t>Mapped from ALQC</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1138,6 +1233,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1148,6 +1244,10 @@
           <t>Mapped from ALQT</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1170,6 +1270,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1180,6 +1281,10 @@
           <t>Mapped from ALS1</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1202,6 +1307,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1212,6 +1318,10 @@
           <t>Mapped from M9ALTS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1234,6 +1344,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1244,6 +1355,10 @@
           <t>Mapped from ALUC</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1266,6 +1381,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1276,6 +1392,10 @@
           <t>Mapped from ALUN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1298,6 +1418,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1308,6 +1429,10 @@
           <t>Mapped from AMCS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1330,6 +1455,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1340,6 +1466,10 @@
           <t>Mapped from CRI1</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1362,6 +1492,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1372,6 +1503,10 @@
           <t>Mapped from AMPT</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1394,6 +1529,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1404,6 +1540,10 @@
           <t>Mapped from M9APPR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1426,6 +1566,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1436,6 +1577,10 @@
           <t>Mapped from ARPA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1458,6 +1603,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1468,6 +1614,10 @@
           <t>Mapped from ARPR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1490,6 +1640,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1500,6 +1651,10 @@
           <t>Mapped from ARR1</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1522,6 +1677,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1532,6 +1688,10 @@
           <t>Mapped from ATMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1554,6 +1714,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1564,6 +1725,10 @@
           <t>Mapped from ATMO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1586,6 +1751,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1596,6 +1762,10 @@
           <t>Mapped from M9ATTC</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1618,6 +1788,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1628,6 +1799,10 @@
           <t>Mapped from M9AUGE</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1650,6 +1825,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1660,6 +1836,10 @@
           <t>Mapped from AUTC</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1682,6 +1862,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1692,6 +1873,10 @@
           <t>Mapped from AVAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1714,6 +1899,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1724,6 +1910,10 @@
           <t>Mapped from AVST</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1746,6 +1936,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1756,6 +1947,10 @@
           <t>Mapped from AWDY</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1778,6 +1973,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1788,6 +1984,10 @@
           <t>Mapped from BACD</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1810,6 +2010,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1820,6 +2021,10 @@
           <t>Mapped from BBTM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1842,6 +2047,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1852,6 +2058,10 @@
           <t>Mapped from BGRP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1874,6 +2084,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1884,6 +2095,10 @@
           <t>Mapped from BOGR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1906,6 +2121,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1916,6 +2132,10 @@
           <t>Mapped from BPEY</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1938,6 +2158,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1948,6 +2169,10 @@
           <t>Mapped from BUAR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2005,6 +2230,10 @@
           <t>Mapped from BUYE</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2027,6 +2256,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2037,6 +2267,10 @@
           <t>Mapped from BYPR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2059,6 +2293,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2069,6 +2304,10 @@
           <t>Mapped from M9CAWC</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2091,6 +2330,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2101,6 +2341,10 @@
           <t>Mapped from CAWT</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2123,6 +2367,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2133,6 +2378,10 @@
           <t>Mapped from CCCM</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2155,6 +2404,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2165,6 +2415,10 @@
           <t>Mapped from CCI1</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2187,6 +2441,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2197,6 +2452,10 @@
           <t>Mapped from CCO1</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2219,6 +2478,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2229,6 +2489,10 @@
           <t>Mapped from CCO2</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2251,6 +2515,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2261,6 +2526,10 @@
           <t>Mapped from CCO3</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2283,6 +2552,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2293,6 +2563,10 @@
           <t>Mapped from CDYN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2315,6 +2589,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2325,6 +2600,10 @@
           <t>Mapped from CETY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2347,6 +2626,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2357,6 +2637,10 @@
           <t>Mapped from CFI1</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2379,6 +2663,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2389,6 +2674,10 @@
           <t>Mapped from CFI2</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2411,6 +2700,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2421,6 +2711,10 @@
           <t>Mapped from CFI3</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2443,6 +2737,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2453,6 +2748,10 @@
           <t>Mapped from CFI4</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2475,6 +2774,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2485,6 +2785,10 @@
           <t>Mapped from CFI5</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2507,6 +2811,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2517,6 +2822,10 @@
           <t>Mapped from CHCD</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2539,6 +2848,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2549,6 +2859,10 @@
           <t>Mapped from M9COCD</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2571,6 +2885,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2581,6 +2896,10 @@
           <t>Mapped from M9COFA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2603,6 +2922,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2613,6 +2933,10 @@
           <t>Mapped from COMG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2635,6 +2959,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2645,6 +2970,10 @@
           <t>Mapped from CONC</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2657,6 +2986,7 @@
           <t>CPCD</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>PYTHON</t>
@@ -2681,6 +3011,10 @@
           <t>Mapped from CPCD</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2703,6 +3037,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2713,6 +3048,10 @@
           <t>Mapped from M9CPDC</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2735,6 +3074,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2745,6 +3085,10 @@
           <t>Mapped from CPGR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2767,6 +3111,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2777,6 +3122,10 @@
           <t>Mapped from M9CPL0</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2799,6 +3148,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2809,6 +3159,10 @@
           <t>Mapped from M9CPL1</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2831,6 +3185,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2841,6 +3196,10 @@
           <t>Mapped from M9CPL2</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2853,6 +3212,7 @@
           <t>CPRE</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2873,6 +3233,10 @@
           <t>Mapped from M9CPRE</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2885,6 +3249,7 @@
           <t>CPRI</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2905,6 +3270,10 @@
           <t>Mapped from M9CPRI</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2927,6 +3296,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2937,6 +3307,10 @@
           <t>Mapped from CPUN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2959,6 +3333,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2969,6 +3344,10 @@
           <t>Mapped from CQUQ</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2991,6 +3370,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3001,6 +3381,10 @@
           <t>Mapped from CRI1</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3023,6 +3407,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3033,6 +3418,10 @@
           <t>Mapped from CRJQ</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3055,6 +3444,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3065,6 +3455,10 @@
           <t>Mapped from M9CRTM</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3087,6 +3481,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3097,6 +3492,10 @@
           <t>Mapped from CSLV</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3119,6 +3518,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3129,6 +3529,10 @@
           <t>Mapped from M9CSNO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3151,6 +3555,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3161,6 +3566,10 @@
           <t>Mapped from CSTQ</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3183,6 +3592,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3193,6 +3603,10 @@
           <t>Mapped from CUCD</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3215,6 +3629,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3225,6 +3640,10 @@
           <t>Mapped from CUCS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3247,6 +3666,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3257,6 +3677,10 @@
           <t>Mapped from CWUN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3279,6 +3703,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3289,6 +3714,10 @@
           <t>Mapped from DCCD</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3311,6 +3740,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3321,6 +3751,10 @@
           <t>Mapped from DDEX</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3343,6 +3777,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3353,6 +3788,10 @@
           <t>Mapped from DDLO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3375,6 +3814,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3385,6 +3825,10 @@
           <t>Mapped from M9DICM</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3407,6 +3851,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3417,6 +3862,10 @@
           <t>Mapped from M9DIDF</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3439,6 +3888,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3449,6 +3899,10 @@
           <t>Mapped from M9DIDY</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3471,6 +3925,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3481,6 +3936,10 @@
           <t>Mapped from DIGI</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3503,6 +3962,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3513,6 +3973,10 @@
           <t>Mapped from DIGR</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3535,6 +3999,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3545,6 +4010,10 @@
           <t>Mapped from DILE</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3567,6 +4036,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3577,6 +4047,10 @@
           <t>Mapped from DIM1</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3599,6 +4073,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3609,6 +4084,10 @@
           <t>Mapped from DIM2</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3631,6 +4110,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3641,6 +4121,10 @@
           <t>Mapped from DIM3</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3663,6 +4147,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3673,6 +4158,10 @@
           <t>Mapped from DIRR</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3695,6 +4184,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3705,6 +4195,10 @@
           <t>Mapped from DITI</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3727,6 +4221,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3737,6 +4232,10 @@
           <t>Mapped from M9DLEF</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3759,6 +4258,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3769,6 +4269,10 @@
           <t>Mapped from M9DLET</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3806,6 +4310,10 @@
           <t>Mapped from DMFN</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3847,6 +4355,10 @@
           <t>Mapped from DPID</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3869,6 +4381,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3879,6 +4392,10 @@
           <t>Mapped from DPLO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3901,6 +4418,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3911,6 +4429,10 @@
           <t>Mapped from DWNO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3933,6 +4455,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3943,6 +4466,10 @@
           <t>Mapped from M9ECAR</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3965,6 +4492,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3975,6 +4503,10 @@
           <t>Mapped from M9ECCC</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3997,6 +4529,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4007,6 +4540,10 @@
           <t>Mapped from ECMA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4029,6 +4566,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4039,6 +4577,10 @@
           <t>Mapped from ECVE</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4083,6 +4625,10 @@
           <t>Mapped from EOQM</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4105,6 +4651,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4115,6 +4662,10 @@
           <t>Mapped from EOQT</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4137,6 +4688,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4147,6 +4699,10 @@
           <t>Mapped from EPCD</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4169,6 +4725,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4179,6 +4736,10 @@
           <t>Mapped from EQDA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4201,6 +4762,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4211,6 +4773,10 @@
           <t>Mapped from ETRF</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4233,6 +4799,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4243,6 +4810,10 @@
           <t>Mapped from EVGR</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4265,6 +4836,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4275,6 +4847,10 @@
           <t>Mapped from EXCA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4297,6 +4873,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4307,6 +4884,10 @@
           <t>Mapped from EXPD</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4344,6 +4925,10 @@
           <t>Mapped from M9FACI</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4356,11 +4941,13 @@
           <t>FANO</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4371,6 +4958,10 @@
           <t>Mapped from M9FANO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4383,11 +4974,13 @@
           <t>FANQ</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4398,6 +4991,10 @@
           <t>Mapped from M9FANQ</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4410,11 +5007,13 @@
           <t>FANR</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4425,6 +5024,10 @@
           <t>Mapped from M9FANR</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4447,6 +5050,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4457,6 +5061,10 @@
           <t>Mapped from M9FATM</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4479,6 +5087,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4489,6 +5098,10 @@
           <t>Mapped from FCCM</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4511,6 +5124,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4521,6 +5135,10 @@
           <t>Mapped from FCU1</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4543,6 +5161,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4553,6 +5172,10 @@
           <t>Mapped from FEBA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4575,6 +5198,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4585,6 +5209,10 @@
           <t>Mapped from FRAG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4607,6 +5235,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4617,6 +5246,10 @@
           <t>Mapped from FRE3</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4639,6 +5272,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4649,6 +5283,10 @@
           <t>Mapped from FRE4</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4671,6 +5309,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4681,6 +5320,10 @@
           <t>Mapped from FSSQ</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4703,6 +5346,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4713,6 +5357,10 @@
           <t>Mapped from FUDS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4735,6 +5383,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4745,6 +5394,10 @@
           <t>Mapped from FUNC</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4767,6 +5420,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4777,6 +5431,10 @@
           <t>Mapped from GRMT</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4799,6 +5457,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4809,6 +5468,10 @@
           <t>Mapped from GRP1</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4831,6 +5494,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4841,6 +5505,10 @@
           <t>Mapped from GRP2</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4863,6 +5531,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4873,6 +5542,10 @@
           <t>Mapped from GRP3</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4895,6 +5568,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4905,6 +5579,10 @@
           <t>Mapped from GRP4</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4927,6 +5605,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4937,6 +5616,10 @@
           <t>Mapped from GRP5</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4959,6 +5642,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4969,6 +5653,10 @@
           <t>Mapped from GRTI</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4991,6 +5679,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5001,6 +5690,10 @@
           <t>Mapped from GRTS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5023,6 +5716,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5033,6 +5727,10 @@
           <t>Mapped from GRWE</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5055,6 +5753,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5065,6 +5764,10 @@
           <t>Mapped from HAC1</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5087,6 +5790,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5097,6 +5801,10 @@
           <t>Mapped from HAC2</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5119,6 +5827,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5129,6 +5838,10 @@
           <t>Mapped from HAC3</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5151,6 +5864,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5161,6 +5875,10 @@
           <t>Mapped from HAZI</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5183,6 +5901,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5193,6 +5912,10 @@
           <t>Mapped from HIE1</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5215,6 +5938,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5225,6 +5949,10 @@
           <t>Mapped from HIE2</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5247,6 +5975,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5257,6 +5986,10 @@
           <t>Mapped from HIE3</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5279,6 +6012,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5289,6 +6023,10 @@
           <t>Mapped from HIE4</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5311,6 +6049,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5321,6 +6060,10 @@
           <t>Mapped from HIE5</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5343,6 +6086,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5353,6 +6097,10 @@
           <t>Mapped from HVMT</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5375,6 +6123,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5385,6 +6134,10 @@
           <t>Mapped from IDDT</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5407,6 +6160,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5417,6 +6171,10 @@
           <t>Mapped from IHEI</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5439,6 +6197,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5449,6 +6208,10 @@
           <t>Mapped from ILEN</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5471,6 +6234,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5481,6 +6245,10 @@
           <t>Mapped from INCD</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5503,6 +6271,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5513,6 +6282,10 @@
           <t>Mapped from INDI</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5535,6 +6308,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5545,6 +6319,10 @@
           <t>Mapped from INDT</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5567,6 +6345,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5577,6 +6356,10 @@
           <t>Mapped from INSC</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5599,6 +6382,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5609,6 +6393,10 @@
           <t>Mapped from INSH</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5631,6 +6419,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5641,6 +6430,10 @@
           <t>Mapped from INSL</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5663,6 +6456,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5673,6 +6467,10 @@
           <t>Mapped from IPLA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5695,6 +6493,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5705,6 +6504,10 @@
           <t>Mapped from ISEG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5727,6 +6530,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5737,6 +6541,10 @@
           <t>Mapped from ITCL</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5759,6 +6567,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5769,6 +6578,10 @@
           <t>Mapped from ITDS</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5791,6 +6604,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5801,6 +6615,10 @@
           <t>Mapped from ITGR</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5823,6 +6641,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5833,6 +6652,10 @@
           <t>Mapped from ITNE</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5872,6 +6695,10 @@
           <t>Mapped from M9ITNO</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5894,6 +6721,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5904,6 +6732,10 @@
           <t>Mapped from ITRF</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5926,6 +6758,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5936,6 +6769,10 @@
           <t>Mapped from ITRU</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5958,6 +6795,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5968,6 +6806,10 @@
           <t>Mapped from ITTY</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5990,6 +6832,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6000,6 +6843,10 @@
           <t>Mapped from IWID</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6022,6 +6869,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6032,6 +6880,10 @@
           <t>Mapped from M9JITF</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6054,6 +6906,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6064,6 +6917,10 @@
           <t>Mapped from KTEX</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6086,6 +6943,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6096,6 +6954,10 @@
           <t>Mapped from M9LAMA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6118,6 +6980,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6128,6 +6991,10 @@
           <t>Mapped from LEA1</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6150,6 +7017,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6160,6 +7028,10 @@
           <t>Mapped from LEA2</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6182,6 +7054,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6192,6 +7065,10 @@
           <t>Mapped from LEA3</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6214,6 +7091,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6224,6 +7102,10 @@
           <t>Mapped from M9LEA4</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6246,6 +7128,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6256,6 +7139,10 @@
           <t>Mapped from LEAI</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6278,6 +7165,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6288,6 +7176,10 @@
           <t>Mapped from LEAT</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6310,6 +7202,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6320,6 +7213,10 @@
           <t>Mapped from LEVD</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6342,6 +7239,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6352,6 +7250,10 @@
           <t>Mapped from LEVL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6374,6 +7276,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6384,6 +7287,10 @@
           <t>Mapped from LOQT</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6406,6 +7313,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6416,6 +7324,10 @@
           <t>Mapped from LYQT</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6438,6 +7350,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6448,6 +7361,10 @@
           <t>Mapped from MABC</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6470,6 +7387,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6480,6 +7398,10 @@
           <t>Mapped from MABU</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6502,6 +7424,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6512,6 +7435,10 @@
           <t>Mapped from MAPL</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6534,6 +7461,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6544,6 +7472,10 @@
           <t>Mapped from MAPN</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6566,6 +7498,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6576,6 +7509,10 @@
           <t>Mapped from M9MARC</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6598,6 +7535,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6608,6 +7546,10 @@
           <t>Mapped from MBFR</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6630,6 +7572,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6640,6 +7583,10 @@
           <t>Mapped from MBSR</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6662,6 +7609,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6672,6 +7620,10 @@
           <t>Mapped from MBUR</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6694,6 +7646,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6704,6 +7657,10 @@
           <t>Mapped from MDIR</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6726,6 +7683,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6736,6 +7694,10 @@
           <t>Mapped from MES1</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6758,6 +7720,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6768,6 +7731,10 @@
           <t>Mapped from MES2</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6790,6 +7757,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6800,6 +7768,10 @@
           <t>Mapped from MES3</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6822,6 +7794,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6832,6 +7805,10 @@
           <t>Mapped from MES4</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6854,6 +7831,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6864,6 +7842,10 @@
           <t>Mapped from MOCM</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6886,6 +7868,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6896,6 +7879,10 @@
           <t>Mapped from M9MOLL</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6918,6 +7905,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6928,6 +7916,10 @@
           <t>Mapped from MOQT</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6950,6 +7942,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6960,6 +7953,10 @@
           <t>Mapped from MOTP</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6982,6 +7979,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6992,6 +7990,10 @@
           <t>Mapped from MPCD</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7014,6 +8016,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7024,6 +8027,10 @@
           <t>Mapped from MPCT</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7046,6 +8053,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7056,6 +8064,10 @@
           <t>Mapped from MPGM</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7078,6 +8090,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7088,6 +8101,10 @@
           <t>Mapped from MRQT</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7110,6 +8127,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7120,6 +8138,10 @@
           <t>Mapped from MSCH</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7142,6 +8164,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7152,6 +8175,10 @@
           <t>Mapped from MVA1</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7174,6 +8201,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7184,6 +8212,10 @@
           <t>Mapped from MVA2</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7206,6 +8238,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7216,6 +8249,10 @@
           <t>Mapped from MVA3</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7238,6 +8275,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7248,6 +8286,10 @@
           <t>Mapped from MVA4</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7270,6 +8312,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7280,6 +8323,10 @@
           <t>Mapped from MXPC</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7302,6 +8349,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7312,6 +8360,10 @@
           <t>Mapped from MXSM</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7334,6 +8386,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7344,6 +8397,10 @@
           <t>Mapped from MXST</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7366,6 +8423,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7376,6 +8434,10 @@
           <t>Mapped from NESA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7398,6 +8460,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7408,6 +8471,10 @@
           <t>Mapped from NEWE</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7430,6 +8497,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7440,6 +8508,10 @@
           <t>Mapped from NPTO</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7462,6 +8534,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7472,6 +8545,10 @@
           <t>Mapped from NSUF</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7494,6 +8571,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7504,6 +8582,10 @@
           <t>Mapped from NUIN</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7526,6 +8608,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7536,6 +8619,10 @@
           <t>Mapped from NUS7</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7558,6 +8645,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7568,6 +8656,10 @@
           <t>Mapped from ODDT</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7590,6 +8682,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7600,6 +8693,10 @@
           <t>Mapped from M9OPFQ</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7640,6 +8737,10 @@
           <t>Mapped from OPLC</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7662,6 +8763,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7672,6 +8774,10 @@
           <t>Mapped from OPOM</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7694,6 +8800,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7704,6 +8811,10 @@
           <t>Mapped from M9ORCO</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7726,6 +8837,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7736,6 +8848,10 @@
           <t>Mapped from ORQT</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7780,6 +8896,10 @@
           <t>Mapped from ORTY</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7802,6 +8922,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7812,6 +8933,10 @@
           <t>Mapped from OTDI</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7834,6 +8959,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7844,6 +8970,10 @@
           <t>Mapped from PAFL</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7866,6 +8996,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7876,6 +9007,10 @@
           <t>Mapped from PDCC</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7898,6 +9033,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7908,6 +9044,10 @@
           <t>Mapped from PDLN</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7930,6 +9070,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7940,6 +9081,10 @@
           <t>Mapped from PEQ1</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7962,6 +9107,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7972,6 +9118,10 @@
           <t>Mapped from PEQ2</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7994,6 +9144,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8004,6 +9155,10 @@
           <t>Mapped from PEQ3</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8026,6 +9181,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8036,6 +9192,10 @@
           <t>Mapped from PEQ4</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8058,6 +9218,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8068,6 +9229,10 @@
           <t>Mapped from PET1</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8090,6 +9255,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8100,6 +9266,10 @@
           <t>Mapped from PET2</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8122,6 +9292,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8132,6 +9303,10 @@
           <t>Mapped from PET3</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8154,6 +9329,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8164,6 +9340,10 @@
           <t>Mapped from PET4</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8201,6 +9381,10 @@
           <t>Mapped from PFTM</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8223,6 +9407,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8233,6 +9418,10 @@
           <t>Mapped from PISE</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8255,6 +9444,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8265,6 +9455,10 @@
           <t>Mapped from M9PLAP</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8289,17 +9483,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>itno = str(row.get("ITNO", row.get("MMITNO", ""))).strip().upper()
+          <t>itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
 itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
-puit = str(row.get("PUIT", row.get("MMPUIT", ""))).strip()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+# Priority 1
+if puit == "3":
+    return "05"
+# Priority 2
 if itno.startswith(("RS9", "ZZ")):
     return "00"
+# Future ITTY logic
 if itty in ("RM", "PK") and puit == "2":
     return "01"
 if itty in ("SF", "FG") and puit == "1":
     return "02"
-if puit == "3":
-    return "05"
+# Fallback
 if source is None or str(source).strip() == "":
     return ""
 return str(source).zfill(2)</t>
@@ -8315,6 +9515,10 @@
           <t>Mapped from PLCD</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8352,6 +9556,10 @@
           <t>Mapped from PLHZ</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8374,6 +9582,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8384,6 +9593,10 @@
           <t>Mapped from PLMZ</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8406,6 +9619,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8416,6 +9630,10 @@
           <t>Mapped from M9PLUP</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8438,6 +9656,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8448,6 +9667,10 @@
           <t>Mapped from POCY</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8470,6 +9693,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8480,6 +9704,10 @@
           <t>Mapped from POOT</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8502,6 +9730,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8512,6 +9741,10 @@
           <t>Mapped from PPDT</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8534,6 +9767,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8544,6 +9778,10 @@
           <t>Mapped from M9PPL0</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8566,6 +9804,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8576,6 +9815,10 @@
           <t>Mapped from M9PPL1</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8598,6 +9841,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8608,6 +9852,10 @@
           <t>Mapped from M9PPL2</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8630,6 +9878,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8640,6 +9889,10 @@
           <t>Mapped from PPUN</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8662,6 +9915,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8672,6 +9926,10 @@
           <t>Mapped from PRCD</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8684,6 +9942,7 @@
           <t>PRCM</t>
         </is>
       </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -8704,6 +9963,10 @@
           <t>Mapped from M9PRCM</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8726,6 +9989,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8736,6 +10000,10 @@
           <t>Mapped from PRGP</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8758,6 +10026,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8768,6 +10037,10 @@
           <t>Mapped from PRGR</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8790,6 +10063,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8800,6 +10074,10 @@
           <t>Mapped from PRIF</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8822,6 +10100,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8832,6 +10111,10 @@
           <t>Mapped from PROD</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8854,6 +10137,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8864,6 +10148,10 @@
           <t>Mapped from M9PRRA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8876,6 +10164,7 @@
           <t>PRVG</t>
         </is>
       </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -8896,6 +10185,10 @@
           <t>Mapped from PRVG</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8918,6 +10211,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8928,6 +10222,10 @@
           <t>Mapped from PUCD</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8976,6 +10274,10 @@
           <t>Mapped from PUIT</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8998,6 +10300,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9008,6 +10311,10 @@
           <t>Mapped from PUPR</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9030,6 +10337,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9040,6 +10348,10 @@
           <t>Mapped from PUUN</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9062,6 +10374,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9072,6 +10385,10 @@
           <t>Mapped from QACD</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9094,6 +10411,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9104,6 +10422,10 @@
           <t>Mapped from QIRQ</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9126,6 +10448,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9136,6 +10459,10 @@
           <t>Mapped from QMGP</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9158,6 +10485,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9168,6 +10496,10 @@
           <t>Mapped from M9QUCW</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9190,6 +10522,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9200,6 +10533,10 @@
           <t>Mapped from QUQT</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9222,6 +10559,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9232,6 +10570,10 @@
           <t>Mapped from REDY</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9254,6 +10596,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9264,6 +10607,10 @@
           <t>Mapped from REMN</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9286,6 +10633,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9296,6 +10644,10 @@
           <t>Mapped from REOP</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9318,6 +10670,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9328,6 +10681,10 @@
           <t>Mapped from REQT</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9385,6 +10742,10 @@
           <t>Manual Edit</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9407,6 +10768,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9417,6 +10779,10 @@
           <t>Mapped from M9REWH</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9439,6 +10805,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9449,6 +10816,10 @@
           <t>Mapped from RIDC</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9471,6 +10842,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9481,6 +10853,10 @@
           <t>Mapped from RIDE</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9503,6 +10879,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9513,6 +10890,10 @@
           <t>Mapped from M9RJCW</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9535,6 +10916,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9545,6 +10927,10 @@
           <t>Mapped from RJQT</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9567,6 +10953,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9577,6 +10964,10 @@
           <t>Mapped from RLQT</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9599,6 +10990,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9609,6 +11001,10 @@
           <t>Mapped from RMSG</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9631,6 +11027,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9641,6 +11038,10 @@
           <t>Mapped from RNRI</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9663,6 +11064,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9673,6 +11075,10 @@
           <t>Mapped from RUID</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9695,6 +11101,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9705,6 +11112,10 @@
           <t>Mapped from SACD</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9727,6 +11138,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9737,6 +11149,10 @@
           <t>Mapped from SAEL</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9759,6 +11175,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9769,6 +11186,10 @@
           <t>Mapped from SAFC</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9791,6 +11212,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9801,6 +11223,10 @@
           <t>Mapped from SALE</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9823,6 +11249,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9833,6 +11260,10 @@
           <t>Mapped from SALM</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9855,6 +11286,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9865,6 +11297,10 @@
           <t>Mapped from SAPR</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9887,6 +11323,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9897,6 +11334,10 @@
           <t>Mapped from SATD</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9919,6 +11360,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9929,6 +11371,10 @@
           <t>Mapped from SCGR</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9951,6 +11397,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9961,6 +11408,10 @@
           <t>Mapped from M9SCMO</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9973,11 +11424,13 @@
           <t>SCPO</t>
         </is>
       </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9988,6 +11441,10 @@
           <t>Mapped from SCPO</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10010,6 +11467,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10020,6 +11478,10 @@
           <t>Mapped from SCRQ</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10042,6 +11504,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10052,6 +11515,10 @@
           <t>Mapped from SESO</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10074,6 +11541,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10084,6 +11552,10 @@
           <t>Mapped from SHCC</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10106,6 +11578,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10116,6 +11589,10 @@
           <t>Mapped from SLDY</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10153,6 +11630,10 @@
           <t>Mapped from SLTP</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10175,6 +11656,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10185,6 +11667,10 @@
           <t>Mapped from SMFI</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10207,6 +11693,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10217,6 +11704,10 @@
           <t>Mapped from M9SOCO</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10239,6 +11730,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10249,6 +11741,10 @@
           <t>Mapped from SODY</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10271,6 +11767,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10281,6 +11778,10 @@
           <t>Mapped from SPAC</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10318,6 +11819,10 @@
           <t>Mapped from SPDT</t>
         </is>
       </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10340,6 +11845,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10350,6 +11856,10 @@
           <t>Mapped from SPE1</t>
         </is>
       </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10372,6 +11882,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10382,6 +11893,10 @@
           <t>Mapped from SPE2</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10404,6 +11919,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10414,6 +11930,10 @@
           <t>Mapped from SPE3</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10436,6 +11956,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10446,6 +11967,10 @@
           <t>Mapped from SPE4</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10468,6 +11993,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10478,6 +12004,10 @@
           <t>Mapped from SPE5</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10500,6 +12030,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10510,6 +12041,10 @@
           <t>Mapped from SPGV</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10532,6 +12067,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10542,6 +12078,10 @@
           <t>Mapped from SPIH</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10564,6 +12104,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10574,6 +12115,10 @@
           <t>Mapped from SPLC</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10596,6 +12141,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10606,6 +12152,10 @@
           <t>Mapped from SPMT</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10645,6 +12195,10 @@
           <t>Mapped from SPUC</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10667,6 +12221,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10677,6 +12232,10 @@
           <t>Mapped from SPUN</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10699,6 +12258,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10709,6 +12269,10 @@
           <t>Mapped from SQC2</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10731,6 +12295,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10741,6 +12306,10 @@
           <t>Mapped from SQC3</t>
         </is>
       </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10763,6 +12332,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10773,6 +12343,10 @@
           <t>Mapped from SQCS</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10795,6 +12369,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10805,6 +12380,10 @@
           <t>Mapped from SSDA</t>
         </is>
       </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10827,6 +12406,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10837,6 +12417,10 @@
           <t>Mapped from SSMT</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10859,6 +12443,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10869,6 +12454,10 @@
           <t>Mapped from SSQT</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10891,6 +12480,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10901,6 +12491,10 @@
           <t>Mapped from SSRE</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10913,6 +12507,7 @@
           <t>STAT</t>
         </is>
       </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -10933,6 +12528,10 @@
           <t>Mapped from STAT</t>
         </is>
       </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10955,6 +12554,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10965,6 +12565,10 @@
           <t>Mapped from STCD</t>
         </is>
       </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10987,6 +12591,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10997,6 +12602,10 @@
           <t>Mapped from STCN</t>
         </is>
       </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11019,6 +12628,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11029,6 +12639,10 @@
           <t>Mapped from M9STCW</t>
         </is>
       </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11051,6 +12665,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11061,6 +12676,10 @@
           <t>Mapped from STMT</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11083,6 +12702,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11093,6 +12713,10 @@
           <t>Mapped from STNC</t>
         </is>
       </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11115,6 +12739,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11125,6 +12750,10 @@
           <t>Mapped from STQT</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11162,6 +12791,10 @@
           <t>Mapped from STRL</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11184,6 +12817,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11194,6 +12828,10 @@
           <t>Mapped from STTX</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11216,6 +12854,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11226,6 +12865,10 @@
           <t>Mapped from STUN</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11248,6 +12891,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11258,6 +12902,10 @@
           <t>Mapped from SUME</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11280,6 +12928,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11290,6 +12939,10 @@
           <t>Mapped from SUMP</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11327,6 +12980,10 @@
           <t>Mapped from SUNO</t>
         </is>
       </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11349,6 +13006,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11359,6 +13017,10 @@
           <t>Mapped from SURT</t>
         </is>
       </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11381,6 +13043,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11391,6 +13054,10 @@
           <t>Mapped from SUWH</t>
         </is>
       </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11428,6 +13095,10 @@
           <t>Mapped from SVEI</t>
         </is>
       </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11450,6 +13121,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11460,6 +13132,10 @@
           <t>Mapped from TANK</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11482,6 +13158,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11492,6 +13169,10 @@
           <t>Mapped from TAXC</t>
         </is>
       </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11514,6 +13195,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11524,6 +13206,10 @@
           <t>Mapped from TBFR</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11546,6 +13232,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11556,6 +13243,10 @@
           <t>Mapped from TBSR</t>
         </is>
       </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11578,6 +13269,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11588,6 +13280,10 @@
           <t>Mapped from TBUR</t>
         </is>
       </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11610,6 +13306,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11620,6 +13317,10 @@
           <t>Mapped from TECR</t>
         </is>
       </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11642,6 +13343,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11652,6 +13354,10 @@
           <t>Mapped from TOHI</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11689,6 +13395,10 @@
           <t>Mapped from TOMU</t>
         </is>
       </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11711,6 +13421,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11721,6 +13432,10 @@
           <t>Mapped from TORE</t>
         </is>
       </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11743,6 +13458,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11753,6 +13469,10 @@
           <t>Mapped from TPCD</t>
         </is>
       </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11775,6 +13495,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11785,6 +13506,10 @@
           <t>Mapped from TPLI</t>
         </is>
       </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11807,6 +13532,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11817,6 +13543,10 @@
           <t>Mapped from TRPA</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11829,11 +13559,13 @@
           <t>UCOS</t>
         </is>
       </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>CONST</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11844,6 +13576,10 @@
           <t>Mapped from M9UCOS</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11866,6 +13602,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11876,6 +13613,10 @@
           <t>Mapped from UNMS</t>
         </is>
       </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11898,6 +13639,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11908,6 +13650,10 @@
           <t>Mapped from UNMU</t>
         </is>
       </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11930,6 +13676,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11940,6 +13687,10 @@
           <t>Mapped from UNNN</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11962,6 +13713,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -11972,6 +13724,10 @@
           <t>Mapped from UNPA</t>
         </is>
       </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11994,6 +13750,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12004,6 +13761,10 @@
           <t>Mapped from USYE</t>
         </is>
       </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12043,6 +13804,10 @@
           <t>Mapped from M9VAMT</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12065,6 +13830,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12075,6 +13841,10 @@
           <t>Mapped from VOL3</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12097,6 +13867,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12107,6 +13878,10 @@
           <t>Mapped from VTCP</t>
         </is>
       </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12129,6 +13904,7 @@
           <t>IGNORE</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12139,6 +13915,10 @@
           <t>Mapped from VTCS</t>
         </is>
       </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12161,6 +13941,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12171,6 +13952,10 @@
           <t>Mapped from WADY</t>
         </is>
       </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12193,6 +13978,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12203,6 +13989,10 @@
           <t>Mapped from WAL1</t>
         </is>
       </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12225,6 +14015,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12235,6 +14026,10 @@
           <t>Mapped from WAL2</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12257,6 +14052,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12267,6 +14063,10 @@
           <t>Mapped from WAL3</t>
         </is>
       </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12289,6 +14089,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12299,6 +14100,10 @@
           <t>Mapped from WAL4</t>
         </is>
       </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12321,6 +14126,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12331,6 +14137,10 @@
           <t>Mapped from WAPC</t>
         </is>
       </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12353,6 +14163,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12363,6 +14174,10 @@
           <t>Mapped from M9WCLN</t>
         </is>
       </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12385,6 +14200,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12395,6 +14211,10 @@
           <t>Mapped from WHLO</t>
         </is>
       </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12432,6 +14252,10 @@
           <t>Mapped from WHLT</t>
         </is>
       </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12454,6 +14278,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12464,6 +14289,10 @@
           <t>Mapped from WHSL</t>
         </is>
       </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12501,6 +14330,10 @@
           <t>Mapped from WHSY</t>
         </is>
       </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12538,6 +14371,10 @@
           <t>Mapped from WHTY</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12560,6 +14397,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12570,6 +14408,10 @@
           <t>Mapped from M9WSCA</t>
         </is>
       </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12592,6 +14434,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12602,6 +14445,10 @@
           <t>Mapped from YEQM</t>
         </is>
       </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12624,6 +14471,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12634,6 +14482,10 @@
           <t>Mapped from YEQT</t>
         </is>
       </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12656,6 +14508,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -12666,6 +14519,10 @@
           <t>Mapped from ZCAC</t>
         </is>
       </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12912,7 +14769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18767,6 +20624,238 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:03:24</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MMITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MMPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'-&gt;'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MBITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:50</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MBITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'-&gt;'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MBITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:41:06</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MBITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'-&gt;'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+# CASE WHEN
+if itno.startswith("RS9") or itno.endswith("ZZ"):
+    result = "00"
+elif puit == "3":
+    result = "05"
+elif itty in ("RM", "PK") and puit == "2":
+    result = "01"
+elif itty in ("SF", "FG") and puit == "1":
+    result = "02"
+elif source is None or str(source).strip() == "":
+    result = ""
+else:
+    result = str(source).zfill(2)
+return result'</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:45:40</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+# CASE WHEN
+if itno.startswith("RS9") or itno.endswith("ZZ"):
+    result = "00"
+elif puit == "3":
+    result = "05"
+elif itty in ("RM", "PK") and puit == "2":
+    result = "01"
+elif itty in ("SF", "FG") and puit == "1":
+    result = "02"
+elif source is None or str(source).strip() == "":
+    result = ""
+else:
+    result = str(source).zfill(2)
+return result'-&gt;'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+# Priority 1
+if puit == "3":
+    return "05"
+# Priority 2
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+# Future ITTY logic
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+# Fallback
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/rules/.history/MMS200MI.xlsx
+++ b/config/rules/.history/MMS200MI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="_Audit_Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -4063,14 +4063,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
-if puit == "1":
-    return "00"
-if puit == "2":
-    return "11"
-if puit == "3":
-    return "12"
-return ""</t>
+          <t>puit = str(row.get("MBPUIT", "")).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+return {
+    "1": "00",
+    "2": "11",
+    "3": "12"
+}.get(puit, "")</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PUIT</t>
+          <t>MBPUIT</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -7761,13 +7761,13 @@
       <c r="E226" t="inlineStr">
         <is>
           <t>v = str(source).strip()
-if v == "1":
-    return "NOR"
-if v == "2":
-    return "INV"
-if v == "3":
-    return "D22"
-return v</t>
+if v.endswith(".0"):
+    v = v[:-2]
+return {
+    "1": "NOR",
+    "2": "INV",
+    "3": "D22"
+}.get(v, v)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8289,9 +8289,11 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>itno = str(row.get("ITNO", row.get("MMITNO", ""))).strip().upper()
-itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
-puit = str(row.get("PUIT", row.get("MMPUIT", ""))).strip()
+          <t>itno = str(row.get("MBITNO", row.get("ITNO", ""))).strip().upper()
+itty = str(row.get("MMITTY", row.get("ITTY", ""))).strip().upper()
+puit = str(row.get("MBPUIT", row.get("PUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
 if itno.startswith(("RS9", "ZZ")):
     return "00"
 if itty in ("RM", "PK") and puit == "2":
@@ -8300,9 +8302,7 @@
     return "02"
 if puit == "3":
     return "05"
-if source is None or str(source).strip() == "":
-    return ""
-return str(source).zfill(2)</t>
+return str(source).strip().zfill(2) if str(source).strip() else ""</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8958,10 +8958,10 @@
 if mbsuno == "" and mbsuwh == "":
     return "1"
 # MBSUNO filled
-if mbsuno != "":
+if mbsuno != "" and mbsuwh == "":
     return "2"
 # MBSUWH filled
-if mbsuwh != "":
+if mbsuwh != "" and mbsuno == "":
     return "3"
 return ""</t>
         </is>
@@ -12912,7 +12912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18767,6 +18767,270 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-06-11 14:56:57</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PUIT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Val: 'mbsuno = str(row.get("MBSUNO", "")).strip()
+mbsuwh = str(row.get("MBSUWH", "")).strip()
+# Both blank
+if mbsuno == "" and mbsuwh == "":
+    return "1"
+# MBSUNO filled
+if mbsuno != "":
+    return "2"
+# MBSUWH filled
+if mbsuwh != "":
+    return "3"
+return ""'-&gt;'mbsuno = str(row.get("MBSUNO", "")).strip()
+mbsuwh = str(row.get("MBSUWH", "")).strip()
+# Both blank
+if mbsuno == "" and mbsuwh == "":
+    return "1"
+# MBSUNO filled
+if mbsuno != "" and mbsuwh == "":
+    return "2"
+# MBSUWH filled
+if mbsuwh != "" and mbsuno == "":
+    return "3"
+return ""'</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06-11 15:05:56</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MMITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MMPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'-&gt;'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:14:06</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ORTY</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Src: PUIT-&gt;MBPUIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:16:57</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ORTY</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Val: 'v = str(source).strip()
+if v == "1":
+    return "NOR"
+if v == "2":
+    return "INV"
+if v == "3":
+    return "D22"
+return v'-&gt;'v = str(source).strip()
+if v.endswith(".0"):
+    v = v[:-2]
+return {
+    "1": "NOR",
+    "2": "INV",
+    "3": "D22"
+}.get(v, v)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:48:03</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>EOQM</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Val: 'puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if puit == "1":
+    return "00"
+if puit == "2":
+    return "11"
+if puit == "3":
+    return "12"
+return ""'-&gt;'puit = str(row.get("MBPUIT", "")).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+return {
+    "1": "00",
+    "2": "11",
+    "3": "12"
+}.get(puit, "")'</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:28:32</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PLCD</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Val: 'itno = str(row.get("ITNO", row.get("MBITNO", ""))).strip().upper()
+itty = str(row.get("ITTY", row.get("MMITTY", ""))).strip().upper()
+puit = str(row.get("PUIT", row.get("MBPUIT", ""))).strip()
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+if source is None or str(source).strip() == "":
+    return ""
+return str(source).zfill(2)'-&gt;'itno = str(row.get("MBITNO", row.get("ITNO", ""))).strip().upper()
+itty = str(row.get("MMITTY", row.get("ITTY", ""))).strip().upper()
+puit = str(row.get("MBPUIT", row.get("PUIT", ""))).strip()
+if puit.endswith(".0"):
+    puit = puit[:-2]
+if itno.startswith(("RS9", "ZZ")):
+    return "00"
+if itty in ("RM", "PK") and puit == "2":
+    return "01"
+if itty in ("SF", "FG") and puit == "1":
+    return "02"
+if puit == "3":
+    return "05"
+return str(source).strip().zfill(2) if str(source).strip() else ""'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
